--- a/journal_de_travail/Excel/journal_de_travail_Groupe.xlsx
+++ b/journal_de_travail/Excel/journal_de_travail_Groupe.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/luc_derre_eduvaud_ch/Documents/ES/Rapport/GENLOG 2/Prog_Pj-Loto/journal_de_travail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LDE Github\Prog_Pj-Loto\journal_de_travail\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{37959141-701A-4300-A2BE-1927B5C1ABB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{681E608D-0686-40B9-BC79-60294F44B1FF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{056A0646-7E7E-4407-B302-2EC273959D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D69FA01C-A778-4ABC-B9ED-D1E309CD0B61}"/>
   </bookViews>
@@ -56,7 +56,7 @@
     <t>Discussion du programme principal et modification</t>
   </si>
   <si>
-    <t>Discussion des dernières modification</t>
+    <t>Discussion des dernières modification et de la présentation</t>
   </si>
 </sst>
 </file>
